--- a/visitantes-2.0.xlsx
+++ b/visitantes-2.0.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4283,6 +4283,1358 @@
         <v>46205</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>5714</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:50</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Marcos de Jesud</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>(11) 95429-8069</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5712</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:45</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Maria eliene</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>(11) 97730-7470</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>5713</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:45</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Cristiano Ribeiro</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>(11) 95104-2847</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>5711</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:44</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Mariane</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>(11) 94716-3592</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:43</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>(11) 95811-0696</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5709</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:43</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Rodrigo de Almeida Ramos</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>(11) 97992-8653</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>5710</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:43</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>(11) 94728-9494</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:42</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Paulo Henrique</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>(11) 99633-3162</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>5707</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>26/07/2026 20:42</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Simone</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>(11) 95217-4598</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>5705</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>26/07/2026 12:26</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Beatriz</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>(11) 96240-3769</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>5703</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>26/07/2026 12:25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Ormis Daniel Lagar Videaux</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>(11) 98420-4814</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>5704</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>26/07/2026 12:25</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Débora Cristina dos Santos Alves</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>(11) 98761-6277</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>26/07/2026 12:24</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wanessa alves</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>(11) 96157-0949</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>5694</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:21</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Layana</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>(11) 97736-0498</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>5691</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:18</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Damares</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>(11) 94860-4612</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>5692</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:18</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Edilaine Firminino modesto da Silva</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>(11) 99222-9671</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Café de boas vindas</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>5693</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:18</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Daniele Oliveira</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>(11) 97075-6188</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5688</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:17</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Bianca Fernandes</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>(11) 95989-7085</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:17</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Branda heloise</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>(11) 97725-7808</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>5690</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:17</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Cicero</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>(11) 94899-4186</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>5687</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:16</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Juliana gallet</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>(11) 94897-2704</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>5685</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:14</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Ester</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>(11) 98134-2017</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5686</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:14</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sara Victoria</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>(11) 93942-4160</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5683</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:13</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Matheus</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>(11) 95791-9407</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>5684</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:13</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Shirley cicera</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>(11) 99232-0668</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>5682</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>21/07/2026 22:12</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Suene</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>(11) 95791-4263</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/visitantes-2.0.xlsx
+++ b/visitantes-2.0.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5635,6 +5635,1807 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>5721</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>28/07/2026 20:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Daniele Alves</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>(11) 95432-1479</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5722</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>28/07/2026 20:01</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Gabriel Silva</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>(11) 91938-7966</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5725</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>28/07/2026 22:12</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Igor Rodrigues</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>(11) 98183-5820</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Amigo que teouxe</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>5726</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>28/07/2026 22:14</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Ana Beatriz de Sousa</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>(11) 99625-6915</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>5727</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>28/07/2026 22:14</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Arnold Santod</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>(11) 99012-9844</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>5728</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>28/07/2026 22:15</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Jonathan Oliveira</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>(11) 99012-9844</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Telefone é o do pai dele.
+Jonathan tem 13 anos</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5729</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>28/07/2026 22:15</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Julia Martins</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>(11) 98100-6027</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5733</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>30/07/2026 19:29</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Raquel</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>(11) 98605-3949</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5734</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>30/07/2026 19:51</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Elisabete</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>(11) 99412-7883</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5735</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>30/07/2026 19:53</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Maria Jose</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>(11) 95336-4809</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5736</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:02</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Graziela</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>(11) 94843-7859</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>5737</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:02</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Leticia Nunes</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>(11) 97529-7072</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>5738</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:03</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Elaine Nunes</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>(11) 99916-1637</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>5739</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:03</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Carolina Nunes</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>(11) 93440-2711</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>5740</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:04</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Victor Pires</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>(11) 93019-0788</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>5741</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>30/07/2026 22:04</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Bianca</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>(11) 91147-1403</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>5773</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>01/08/2026 21:48</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>João pedro</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>(11) 96070-8277</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Célula Fervorosos</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>5781</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>02/08/2026 10:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Maria das graças</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>(11) 94507-2092</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>5783</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>02/08/2026 10:20</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Guilherme Alencar</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>(11) 98789-2748</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>5784</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>02/08/2026 10:33</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Micheli Vanessa da Silva</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>(11) 97638-9250</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>5787</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:37</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Diana mendes barbosa</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>(11) 93756-2825</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>5788</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:37</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sandy Silva</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>(11) 98945-6978</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sem célula</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>5789</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:37</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>(11) 91059-1231</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>5790</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:38</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Andressa hata</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>(11) 95279-4939</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sem célula</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>5791</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:38</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Rafaela da silva</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>(11) 95961-6095</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>5792</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:40</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Lorena rodrigues Silva</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>(11) 97682-2219</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>5793</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:40</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Adriana Correia</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>(11) 99629-7486</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sem célula</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>5794</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>02/08/2026 12:40</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Daniel fagner Lima</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>(11) 96809-7307</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>5795</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>02/08/2026 14:39</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>(11) 95961-9065</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Café com os Pastores - primeira vez</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>5799</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:03</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Elaine Odete Oliveira</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Outras Redes Sociais</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>(11) 94254-1317</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>5800</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:04</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Rafael Santos de Oliveira</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>(15) 99178-8533</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>5801</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:05</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Maria leiliane de Araújo Soares</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>(11) 96782-8784</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>5802</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:05</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Lucy Cunha</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>(11) 98312-0810</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>5803</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:05</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Elaine Ferreira</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>(11) 98826-4220</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>5804</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:07</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Jaqueline Martins</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>(11) 98707-1809</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Shalon</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5805</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>02/08/2026 21:09</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Claudenice Santos bezerra</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>(11) 95168-7960</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/visitantes-2.0.xlsx
+++ b/visitantes-2.0.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7436,6 +7436,1606 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5825</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>04/08/2026 19:44</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Daniele</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>(11) 95805-4614</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5826</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>04/08/2026 19:44</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Richard Eduardo</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>(11) 95455-6986</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>5827</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>04/08/2026 19:45</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Izamara Oliveira</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>(11) 95160-3707</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>5828</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>04/08/2026 19:53</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Izabela Oliveira</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>(11) 94853-4548</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5829</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>04/08/2026 19:54</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Chay Santos</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>(11) 96074-2835</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5830</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>04/08/2026 20:03</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Priscila Maia</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>(11) 94014-0303</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>5833</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>04/08/2026 20:23</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Julia SouZa</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>(11) 98649-8430</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>5839</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:05</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Clinton</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>(11) 91038-2440</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>5840</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:11</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Vitoria Alves</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>(11) 98051-5757</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Viu pelo insta</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>5841</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:12</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Franciele Patrícia</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>(11) 95804-8247</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Equipe Avançar</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>5842</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:12</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Eduardo Gabriel</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>(11) 91547-9115</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Amigo trouxe</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>5843</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:13</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Thierry Santiago</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>(11) 99295-5728</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>5844</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:13</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Priscila</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>(11) 94014-0303</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>5845</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:16</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Leonardo dos Anjos Pereira</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>(11) 98125-2655</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>5846</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:22</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Alana Souza Rego</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>(11) 95068-4013</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>5847</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>04/08/2026 22:24</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Joel Magno Marques</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>(11) 96043-2668</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>5867</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>06/08/2026 19:49</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Carolina Romero</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>(11) 95204-6431</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>5868</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>06/08/2026 19:55</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Raquel Aparecida</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>(11) 97994-9897</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>5869</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>06/08/2026 19:59</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Vitoria Andrade</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>(11) 98366-0923</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>5872</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>06/08/2026 21:58</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Caio Alessandro</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>(11) 96078-8455</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5873</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>06/08/2026 22:00</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Victor Silva</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>(11) 93057-2340</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>5874</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>06/08/2026 22:02</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Andrea Santiago</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>(11) 94955-5526</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>5898</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:41</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Gabriel Teixeira</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>(11) 99999-9999</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sem telefone</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>5899</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:42</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Julia vitória</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>(11) 95958-7831</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Coloca no grupo do café</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>5900</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:42</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Davi de Sousa</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>(11) 97635-7990</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>5901</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:43</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Matheus Barbosa</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>(11) 97860-6132</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Coloca no grupo do cafe</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>5902</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:43</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Danilo couras</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>(11) 91677-2759</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Adicionar no grupo do café</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>5903</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>08/08/2026 21:43</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Sophia Andrade queiroz</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>(11) 97716-5405</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>5910</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>09/08/2026 20:52</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Rudnei</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>(75) 99129-0224</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>5911</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>09/08/2026 20:52</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Eud Lima dos Santos</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>(11) 12255-116</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>5912</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>09/08/2026 20:53</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Liz</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>(11) 98197-4405</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>5913</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>09/08/2026 20:54</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Aline</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>(11) 98779-1977</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/visitantes-2.0.xlsx
+++ b/visitantes-2.0.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J170"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9036,6 +9036,856 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>5994</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>11/08/2026 22:15</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Thiago Sales</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>(11) 95317-4608</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Através do Ilson</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>6052</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>13/08/2026 19:22</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Marinalva Da Silva</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>(11) 98161-6220</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>6053</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>13/08/2026 20:01</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Maiara Alves</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>(11) 97315-2718</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>6055</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>13/08/2026 21:59</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Luiz Queiroz</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>(11) 95843-8455</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Célula Marcados</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>6057</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>13/08/2026 22:09</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Yara amorim</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>(11) 96545-6575</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Café de boas vindas</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>6077</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:11</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Debora Cristina</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>(13) 99688-8944</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>6078</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:12</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Miqueias Silva Caetano</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>(11) 96774-3091</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Vai vir mais vezes</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>6079</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:12</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Izaias Francisco dos Santos</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>(11) 95123-0866</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>6080</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:12</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Jennifer Andrade</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Outros</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>(11) 93252-4004</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>6081</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:13</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Jucilene Borges</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>(11) 98355-1074</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Gostou muito</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>6082</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:13</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Paula Santos</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>(11) 96187-7902</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>6083</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>16/08/2026 12:13</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Wagner</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>(11) 95433-6901</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>6090</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>16/08/2026 20:57</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Camila da Silva</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>(11) 97739-7405</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>6091</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>16/08/2026 20:58</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Ana Julia Garcia</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>(11) 96725-1222</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Irma</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>6092</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>16/08/2026 20:58</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Danilo. Costa dos Santos</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>(11) 98907-4637</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>6093</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>16/08/2026 20:58</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Lucas Santos rodrigues</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>(11) 98762-2091</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Irmão</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>6094</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>16/08/2026 20:59</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Carlos Alexandre de Lima</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>(11) 35933-0023</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>

--- a/visitantes-2.0.xlsx
+++ b/visitantes-2.0.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9886,6 +9886,1456 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>6149</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>18/08/2026 22:10</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Sávio</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>(11) 98444-7524</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>6151</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>18/08/2026 22:14</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Sara</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>(11) 95836-0818</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>6185</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:57</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Nelza Laura</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>(11) 97608-3044</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Ela é o filho</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>6187</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:32</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Priscila</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>(11) 94753-8871</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Convidada do Marcos quirinos</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>6188</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:56</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Leidi Costa freitas</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>(11) 95798-3880</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>6193</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:33</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Liliane Guimarães</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>(11) 93010-9470</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Shalom</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>6194</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:34</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Eduarda</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>(11) 95205-3014</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Shalom</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>6195</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:34</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Sthfani cristina</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>(33) 99981-9468</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>6196</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:35</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Cleonice Da Silva Barros</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>(11) 95979-4591</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Neto</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>6197</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:35</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>(11) 96467-8749</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:35</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Lucia Fernanda</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Célula</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>(11) 97479-6141</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Convidada da Ieda</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>6199</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>20/08/2026 22:36</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Bruno Rodrigues</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>(11) 95953-5759</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>6217</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>22/08/2026 21:28</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Arthur Rafael vamos trindade</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>(11) 96042-5830</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>6219</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>23/08/2026 09:23</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Ramiro Mendes Filho</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>(11) 94753-8870</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Domingo da Família</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>6221</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>23/08/2026 09:32</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Mauro Ribeiro da Silva</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>(11) 94532-7023</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Domingo da família</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>6220</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>23/08/2026 09:32</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Cristiane Fuganholi</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>(11) 98168-9358</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Domingo da família</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>23/08/2026 09:35</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Miriã Almeida dos Santos</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>(11) 95127-9305</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Domingo da família</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>6225</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:22</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Letícia Macedo</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>(11) 98451-3640</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Adma</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>6226</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:22</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Geovana Marcelino da Silva Alves</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>(11) 93231-2104</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>6227</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:22</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>(11) 94038-2603</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:22</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Leandro</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>(11) 94038-2603</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>6229</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:23</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Cassandra Dourado</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>(11) 91020-781</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>6230</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>23/08/2026 12:27</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Vanda</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>(11) 95791-4264</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Culto Manhã</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>6233</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>23/08/2026 18:20</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Pietro Miguel</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>(11) 94958-5426</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>6234</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>23/08/2026 18:27</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Vitor Sales</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>(11) 93213-6495</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>23/08/2026 18:29</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Fernanda nadja</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Feminino 🚺</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>(11) 96263-4955</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>6239</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>23/08/2026 20:43</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Anderson Felipe dos Santos</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Passou na Frente</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>(11) 99607-986</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>6240</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>23/08/2026 20:44</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Pedro felicio</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>(11) 95874-4113</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>6241</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Pessoa não cadastrada (CPF: Não informado)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>23/08/2026 20:45</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Romário Mendes</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Masculino 👨</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Amigo/Familiar</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>(11) 98185-6331</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Culto Noite</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
